--- a/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-19T19:31:59+00:00</t>
+    <t>2026-05-20T05:38:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-20T05:38:49+00:00</t>
+    <t>2026-05-21T06:40:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-21T06:40:00+00:00</t>
+    <t>2026-05-22T06:49:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T06:49:05+00:00</t>
+    <t>2026-05-22T08:38:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
+++ b/tiflow-chargeitem/develop/2.0.0-ballot.1/CodeSystem-tiflow-chargeitem-operation-outcome-details-cs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T08:38:10+00:00</t>
+    <t>2026-05-22T11:10:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
